--- a/rover_platform_mbse/export/ROVER-A1-ROVER_ROS-TRACEABILITY-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_ROS-TRACEABILITY-V-001.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SYS-SR x Package'!$A$1:$O$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SWR Trace'!$A$1:$F$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SWR Trace'!$A$1:$F$258</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="1"/>
 </workbook>
@@ -685,7 +685,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>SWR-CRSF-001 SWR-CRSF-002 SWR-CRSF-003 SWR-CRSF-005</t>
+          <t>SWR-CRSF-001 SWR-CRSF-002 SWR-CRSF-003 SWR-CRSF-005 SWR-CRSF-022</t>
         </is>
       </c>
       <c r="F6" s="3" t="n"/>
@@ -698,7 +698,7 @@
       <c r="M6" s="3" t="n"/>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-001 SWR-TRN-002 SWR-TRN-008</t>
+          <t>SWR-TRN-006 SWR-TRN-008 SWR-TRN-023</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -812,7 +812,7 @@
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>SWR-CRSF-012 SWR-CRSF-013</t>
+          <t>SWR-CRSF-012 SWR-CRSF-013 SWR-CRSF-022</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1579,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F259"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3513,27 +3513,27 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-001</t>
+          <t>SWR-CRSF-022</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>rover_description</t>
+          <t>rover_crsf_teleop</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-020</t>
+          <t>SYS-SR-005, SYS-SR-008</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>RoverPlatformArch/.../rover_description</t>
+          <t>RoverPlatformArch/.../rover_crsf_teleop</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>rover_description/test/test_wheel_geometry.py</t>
+          <t>rover_crsf_teleop/test/test_launch_structure.py; rover_crsf_teleop/test/e2e/test_teleop_launch.py</t>
         </is>
       </c>
       <c r="F73" s="3" t="n"/>
@@ -3541,7 +3541,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-002</t>
+          <t>SWR-DESC-001</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-021</t>
+          <t>SYS-SR-020</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -3569,7 +3569,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-003</t>
+          <t>SWR-DESC-002</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -3597,7 +3597,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-004</t>
+          <t>SWR-DESC-003</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-003, SYS-SR-021</t>
+          <t>SYS-SR-021</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>rover_description/test/test_wheel_geometry.py; rover_controller/test/test_wheel_geometry.py</t>
+          <t>rover_description/test/test_wheel_geometry.py</t>
         </is>
       </c>
       <c r="F76" s="3" t="n"/>
@@ -3625,7 +3625,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-005</t>
+          <t>SWR-DESC-004</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-002, SYS-SR-004</t>
+          <t>SYS-SR-003, SYS-SR-021</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>rover_controller/test/test_wheel_geometry.py</t>
+          <t>rover_description/test/test_wheel_geometry.py; rover_controller/test/test_wheel_geometry.py</t>
         </is>
       </c>
       <c r="F77" s="3" t="n"/>
@@ -3653,7 +3653,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-006</t>
+          <t>SWR-DESC-005</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-002, SYS-SR-020</t>
+          <t>SYS-SR-002, SYS-SR-004</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/rover_system/test_rover_a1_system_on_init.cpp</t>
+          <t>rover_controller/test/test_wheel_geometry.py</t>
         </is>
       </c>
       <c r="F78" s="3" t="n"/>
@@ -3681,7 +3681,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-007</t>
+          <t>SWR-DESC-006</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-006, SYS-SR-023</t>
+          <t>SYS-SR-002, SYS-SR-020</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -3699,13 +3699,17 @@
           <t>RoverPlatformArch/.../rover_description</t>
         </is>
       </c>
-      <c r="E79" s="3" t="n"/>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>rover_hardware_interface/test/rover_system/test_rover_a1_system_on_init.cpp</t>
+        </is>
+      </c>
       <c r="F79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-008</t>
+          <t>SWR-DESC-007</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -3715,7 +3719,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-002, SYS-SR-011</t>
+          <t>SYS-SR-006, SYS-SR-023</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -3723,17 +3727,13 @@
           <t>RoverPlatformArch/.../rover_description</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>rover_hardware_interface/test/rover_system/test_rover_a1_system_on_init.cpp</t>
-        </is>
-      </c>
+      <c r="E80" s="3" t="n"/>
       <c r="F80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-009</t>
+          <t>SWR-DESC-008</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-008</t>
+          <t>SYS-SR-002, SYS-SR-011</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -3751,13 +3751,17 @@
           <t>RoverPlatformArch/.../rover_description</t>
         </is>
       </c>
-      <c r="E81" s="3" t="n"/>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>rover_hardware_interface/test/rover_system/test_rover_a1_system_on_init.cpp</t>
+        </is>
+      </c>
       <c r="F81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-010</t>
+          <t>SWR-DESC-009</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3767,7 +3771,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-019</t>
+          <t>SYS-SR-008</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -3775,17 +3779,13 @@
           <t>RoverPlatformArch/.../rover_description</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>rover_hardware_interface/test/rover_sensors/test_phidget_imu_sensor_on_init.cpp</t>
-        </is>
-      </c>
+      <c r="E82" s="3" t="n"/>
       <c r="F82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-011</t>
+          <t>SWR-DESC-010</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-021</t>
+          <t>SYS-SR-019</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -3803,13 +3803,17 @@
           <t>RoverPlatformArch/.../rover_description</t>
         </is>
       </c>
-      <c r="E83" s="3" t="n"/>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>rover_hardware_interface/test/rover_sensors/test_phidget_imu_sensor_on_init.cpp</t>
+        </is>
+      </c>
       <c r="F83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-012</t>
+          <t>SWR-DESC-011</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3819,7 +3823,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-001</t>
+          <t>SYS-SR-021</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -3833,7 +3837,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-013</t>
+          <t>SWR-DESC-012</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3843,7 +3847,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-021</t>
+          <t>SYS-SR-001</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -3857,7 +3861,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-014</t>
+          <t>SWR-DESC-013</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3865,7 +3869,11 @@
           <t>rover_description</t>
         </is>
       </c>
-      <c r="C86" s="3" t="n"/>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-021</t>
+        </is>
+      </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_description</t>
@@ -3877,7 +3885,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-015</t>
+          <t>SWR-DESC-014</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3885,11 +3893,7 @@
           <t>rover_description</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-019</t>
-        </is>
-      </c>
+      <c r="C87" s="3" t="n"/>
       <c r="D87" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_description</t>
@@ -3901,7 +3905,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>SWR-DESC-016</t>
+          <t>SWR-DESC-015</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3911,7 +3915,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-015</t>
+          <t>SYS-SR-019</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -3925,31 +3929,31 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-001</t>
+          <t>SWR-DESC-016</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>rover_diag_manager</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="n"/>
+          <t>rover_description</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-015</t>
+        </is>
+      </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>RoverPlatformArch/.../rover_diag_manager</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>rover_diag_manager/test/integration/test_system_diag_node.cpp; rover_diag_manager/test/unit/test_system_status_msg_conversions.cpp</t>
-        </is>
-      </c>
+          <t>RoverPlatformArch/.../rover_description</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n"/>
       <c r="F89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-002</t>
+          <t>SWR-DIAG-001</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3965,7 +3969,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>rover_diag_manager/test/integration/test_system_diag_node.cpp; rover_diag_manager/test/unit/test_monitor_system_use_case.cpp</t>
+          <t>rover_diag_manager/test/integration/test_system_diag_node.cpp; rover_diag_manager/test/unit/test_system_status_msg_conversions.cpp</t>
         </is>
       </c>
       <c r="F90" s="3" t="n"/>
@@ -3973,7 +3977,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-003</t>
+          <t>SWR-DIAG-002</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3989,7 +3993,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>rover_diag_manager/test/integration/test_system_diag_node.cpp</t>
+          <t>rover_diag_manager/test/integration/test_system_diag_node.cpp; rover_diag_manager/test/unit/test_monitor_system_use_case.cpp</t>
         </is>
       </c>
       <c r="F91" s="3" t="n"/>
@@ -3997,7 +4001,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-004</t>
+          <t>SWR-DIAG-003</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4013,7 +4017,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>rover_diag_manager/test/unit/test_monitor_system_use_case.cpp</t>
+          <t>rover_diag_manager/test/integration/test_system_diag_node.cpp</t>
         </is>
       </c>
       <c r="F92" s="3" t="n"/>
@@ -4021,7 +4025,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-005</t>
+          <t>SWR-DIAG-004</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4029,11 +4033,7 @@
           <t>rover_diag_manager</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-022</t>
-        </is>
-      </c>
+      <c r="C93" s="3" t="n"/>
       <c r="D93" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_diag_manager</t>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>rover_diag_manager/test/integration/test_system_diag_node.cpp; rover_diag_manager/test/unit/test_system_status_msg_conversions.cpp</t>
+          <t>rover_diag_manager/test/unit/test_monitor_system_use_case.cpp</t>
         </is>
       </c>
       <c r="F93" s="3" t="n"/>
@@ -4049,7 +4049,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-006</t>
+          <t>SWR-DIAG-005</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>rover_diag_manager/test/unit/test_system_health_evaluator.cpp; rover_diag_manager/test/integration/test_system_diag_node.cpp</t>
+          <t>rover_diag_manager/test/integration/test_system_diag_node.cpp; rover_diag_manager/test/unit/test_system_status_msg_conversions.cpp</t>
         </is>
       </c>
       <c r="F94" s="3" t="n"/>
@@ -4077,7 +4077,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-007</t>
+          <t>SWR-DIAG-006</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4095,13 +4095,17 @@
           <t>RoverPlatformArch/.../rover_diag_manager</t>
         </is>
       </c>
-      <c r="E95" s="3" t="n"/>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>rover_diag_manager/test/unit/test_system_health_evaluator.cpp; rover_diag_manager/test/integration/test_system_diag_node.cpp</t>
+        </is>
+      </c>
       <c r="F95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-008</t>
+          <t>SWR-DIAG-007</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4109,23 +4113,23 @@
           <t>rover_diag_manager</t>
         </is>
       </c>
-      <c r="C96" s="3" t="n"/>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-022</t>
+        </is>
+      </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_diag_manager</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>rover_diag_manager/test/unit/test_linux_system_metrics_source.cpp; rover_diag_manager/test/unit/test_percentage.cpp; rover_diag_manager/test/unit/test_system_status_msg_conversions.cpp</t>
-        </is>
-      </c>
+      <c r="E96" s="3" t="n"/>
       <c r="F96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-009</t>
+          <t>SWR-DIAG-008</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4133,23 +4137,23 @@
           <t>rover_diag_manager</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-022</t>
-        </is>
-      </c>
+      <c r="C97" s="3" t="n"/>
       <c r="D97" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_diag_manager</t>
         </is>
       </c>
-      <c r="E97" s="3" t="n"/>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>rover_diag_manager/test/unit/test_linux_system_metrics_source.cpp; rover_diag_manager/test/unit/test_percentage.cpp; rover_diag_manager/test/unit/test_system_status_msg_conversions.cpp</t>
+        </is>
+      </c>
       <c r="F97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-010</t>
+          <t>SWR-DIAG-009</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4173,7 +4177,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-011</t>
+          <t>SWR-DIAG-010</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4197,7 +4201,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-012</t>
+          <t>SWR-DIAG-011</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4221,7 +4225,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-013</t>
+          <t>SWR-DIAG-012</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4229,7 +4233,11 @@
           <t>rover_diag_manager</t>
         </is>
       </c>
-      <c r="C101" s="3" t="n"/>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-022</t>
+        </is>
+      </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_diag_manager</t>
@@ -4241,7 +4249,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-014</t>
+          <t>SWR-DIAG-013</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4255,17 +4263,13 @@
           <t>RoverPlatformArch/.../rover_diag_manager</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>rover_diag_manager/test/integration/test_system_diag_node.cpp</t>
-        </is>
-      </c>
+      <c r="E102" s="3" t="n"/>
       <c r="F102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>SWR-DIAG-015</t>
+          <t>SWR-DIAG-014</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4279,41 +4283,37 @@
           <t>RoverPlatformArch/.../rover_diag_manager</t>
         </is>
       </c>
-      <c r="E103" s="3" t="n"/>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>rover_diag_manager/test/integration/test_system_diag_node.cpp</t>
+        </is>
+      </c>
       <c r="F103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-001</t>
+          <t>SWR-DIAG-015</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>rover_gps_heading</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-021</t>
-        </is>
-      </c>
+          <t>rover_diag_manager</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n"/>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>RoverPlatformArch/.../rover_gps_heading</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>rover_gps_heading/test/integration/test_rover_gps_heading_node.cpp</t>
-        </is>
-      </c>
+          <t>RoverPlatformArch/.../rover_diag_manager</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n"/>
       <c r="F104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-002</t>
+          <t>SWR-GPSH-001</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>rover_gps_heading/test/unit/test_gps_msg_conversions.cpp</t>
+          <t>rover_gps_heading/test/integration/test_rover_gps_heading_node.cpp</t>
         </is>
       </c>
       <c r="F105" s="3" t="n"/>
@@ -4341,7 +4341,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-003</t>
+          <t>SWR-GPSH-002</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>rover_gps_heading/test/unit/test_gps_msg_conversions.cpp; rover_gps_heading/test/integration/test_rover_gps_heading_node.cpp</t>
+          <t>rover_gps_heading/test/unit/test_gps_msg_conversions.cpp</t>
         </is>
       </c>
       <c r="F106" s="3" t="n"/>
@@ -4369,7 +4369,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-004</t>
+          <t>SWR-GPSH-003</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>rover_gps_heading/test/unit/test_align_heading_use_case.cpp; rover_gps_heading/test/integration/test_rover_gps_heading_node.cpp</t>
+          <t>rover_gps_heading/test/unit/test_gps_msg_conversions.cpp; rover_gps_heading/test/integration/test_rover_gps_heading_node.cpp</t>
         </is>
       </c>
       <c r="F107" s="3" t="n"/>
@@ -4397,7 +4397,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-005</t>
+          <t>SWR-GPSH-004</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>rover_gps_heading/test/unit/test_heading_alignment_estimator.cpp; rover_gps_heading/test/unit/test_geo_math.cpp</t>
+          <t>rover_gps_heading/test/unit/test_align_heading_use_case.cpp; rover_gps_heading/test/integration/test_rover_gps_heading_node.cpp</t>
         </is>
       </c>
       <c r="F108" s="3" t="n"/>
@@ -4425,7 +4425,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-006</t>
+          <t>SWR-GPSH-005</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>rover_gps_heading/test/unit/test_heading_alignment_estimator.cpp</t>
+          <t>rover_gps_heading/test/unit/test_heading_alignment_estimator.cpp; rover_gps_heading/test/unit/test_geo_math.cpp</t>
         </is>
       </c>
       <c r="F109" s="3" t="n"/>
@@ -4453,7 +4453,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-007</t>
+          <t>SWR-GPSH-006</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>rover_gps_heading/test/unit/test_heading_alignment_estimator.cpp; rover_gps_heading/test/unit/test_gps_msg_conversions.cpp</t>
+          <t>rover_gps_heading/test/unit/test_heading_alignment_estimator.cpp</t>
         </is>
       </c>
       <c r="F110" s="3" t="n"/>
@@ -4481,7 +4481,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-008</t>
+          <t>SWR-GPSH-007</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>rover_gps_heading/test/unit/test_heading_alignment_estimator.cpp</t>
+          <t>rover_gps_heading/test/unit/test_heading_alignment_estimator.cpp; rover_gps_heading/test/unit/test_gps_msg_conversions.cpp</t>
         </is>
       </c>
       <c r="F111" s="3" t="n"/>
@@ -4509,7 +4509,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-009</t>
+          <t>SWR-GPSH-008</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -4517,7 +4517,11 @@
           <t>rover_gps_heading</t>
         </is>
       </c>
-      <c r="C112" s="3" t="n"/>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-021</t>
+        </is>
+      </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_gps_heading</t>
@@ -4525,7 +4529,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>rover_gps_heading/test/unit/test_align_heading_use_case.cpp</t>
+          <t>rover_gps_heading/test/unit/test_heading_alignment_estimator.cpp</t>
         </is>
       </c>
       <c r="F112" s="3" t="n"/>
@@ -4533,7 +4537,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-010</t>
+          <t>SWR-GPSH-009</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -4549,7 +4553,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>rover_gps_heading/test/integration/test_rover_gps_heading_node.cpp; rover_gps_heading/test/unit/test_heading_alignment_estimator.cpp</t>
+          <t>rover_gps_heading/test/unit/test_align_heading_use_case.cpp</t>
         </is>
       </c>
       <c r="F113" s="3" t="n"/>
@@ -4557,7 +4561,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-011</t>
+          <t>SWR-GPSH-010</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -4565,11 +4569,7 @@
           <t>rover_gps_heading</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-022</t>
-        </is>
-      </c>
+      <c r="C114" s="3" t="n"/>
       <c r="D114" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_gps_heading</t>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>rover_gps_heading/test/integration/test_rover_gps_heading_node.cpp</t>
+          <t>rover_gps_heading/test/integration/test_rover_gps_heading_node.cpp; rover_gps_heading/test/unit/test_heading_alignment_estimator.cpp</t>
         </is>
       </c>
       <c r="F114" s="3" t="n"/>
@@ -4585,7 +4585,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-012</t>
+          <t>SWR-GPSH-011</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -4613,7 +4613,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-013</t>
+          <t>SWR-GPSH-012</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -4621,7 +4621,11 @@
           <t>rover_gps_heading</t>
         </is>
       </c>
-      <c r="C116" s="3" t="n"/>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-022</t>
+        </is>
+      </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_gps_heading</t>
@@ -4637,7 +4641,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-014</t>
+          <t>SWR-GPSH-013</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -4653,7 +4657,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>rover_gps_heading/test/integration/test_rover_gps_heading_node.cpp; rover_gps_heading/test/unit/test_heading_alignment_estimator.cpp</t>
+          <t>rover_gps_heading/test/integration/test_rover_gps_heading_node.cpp</t>
         </is>
       </c>
       <c r="F117" s="3" t="n"/>
@@ -4661,7 +4665,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>SWR-GPSH-015</t>
+          <t>SWR-GPSH-014</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -4675,41 +4679,37 @@
           <t>RoverPlatformArch/.../rover_gps_heading</t>
         </is>
       </c>
-      <c r="E118" s="3" t="n"/>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>rover_gps_heading/test/integration/test_rover_gps_heading_node.cpp; rover_gps_heading/test/unit/test_heading_alignment_estimator.cpp</t>
+        </is>
+      </c>
       <c r="F118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-001</t>
+          <t>SWR-GPSH-015</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-002, SYS-SR-020</t>
-        </is>
-      </c>
+          <t>rover_gps_heading</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n"/>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>RoverPlatformArch/.../rover_hardware_interface</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>rover_hardware_interface/test/rover_system/test_rover_a1_system_on_init.cpp</t>
-        </is>
-      </c>
+          <t>RoverPlatformArch/.../rover_gps_heading</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n"/>
       <c r="F119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-002</t>
+          <t>SWR-HWI-001</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-002, SYS-SR-021</t>
+          <t>SYS-SR-002, SYS-SR-020</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/rover_driver/test_phidget_data_transformer.cpp; rover_hardware_interface/test/domain/test_driver_data_snapshot.cpp; rover_hardware_interface/test/rover_driver/test_phidget_motor_driver.cpp</t>
+          <t>rover_hardware_interface/test/rover_system/test_rover_a1_system_on_init.cpp</t>
         </is>
       </c>
       <c r="F120" s="3" t="n"/>
@@ -4737,7 +4737,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-003</t>
+          <t>SWR-HWI-002</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-014</t>
+          <t>SYS-SR-002, SYS-SR-021</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/rover_system/test_rover_a1_system_on_init.cpp; rover_hardware_interface/test/rover_driver/test_phidget_motor_driver.cpp</t>
+          <t>rover_hardware_interface/test/rover_driver/test_phidget_data_transformer.cpp; rover_hardware_interface/test/domain/test_driver_data_snapshot.cpp; rover_hardware_interface/test/rover_driver/test_phidget_motor_driver.cpp</t>
         </is>
       </c>
       <c r="F121" s="3" t="n"/>
@@ -4765,7 +4765,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-004</t>
+          <t>SWR-HWI-003</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-008, SYS-SR-024</t>
+          <t>SYS-SR-014</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/rover_system/test_rover_system_write.cpp; rover_hardware_interface/test/test_utils.cpp</t>
+          <t>rover_hardware_interface/test/rover_system/test_rover_a1_system_on_init.cpp; rover_hardware_interface/test/rover_driver/test_phidget_motor_driver.cpp</t>
         </is>
       </c>
       <c r="F122" s="3" t="n"/>
@@ -4793,7 +4793,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-005</t>
+          <t>SWR-HWI-004</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-007, SYS-SR-008, SYS-SR-014</t>
+          <t>SYS-SR-008, SYS-SR-024</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -4813,19 +4813,15 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/rover_system/test_rover_system_write.cpp; rover_hardware_interface/test/application/test_rover_control_loop_use_case.cpp</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>tEStopLatch/testSwEStopZeroCommandIdealLink</t>
-        </is>
-      </c>
+          <t>rover_hardware_interface/test/rover_system/test_rover_system_write.cpp; rover_hardware_interface/test/test_utils.cpp</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-006</t>
+          <t>SWR-HWI-005</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4835,7 +4831,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-007</t>
+          <t>SYS-SR-007, SYS-SR-008, SYS-SR-014</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -4845,19 +4841,19 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/domain/test_emergency_stop.cpp; rover_hardware_interface/test/rover_safety_controller/test_contact_coil_handler.cpp; rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp</t>
+          <t>rover_hardware_interface/test/rover_system/test_rover_system_write.cpp; rover_hardware_interface/test/application/test_rover_control_loop_use_case.cpp</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>tEStopLatch/testSwEStopNeedsLatchReset</t>
+          <t>tEStopLatch/testSwEStopZeroCommandIdealLink</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-007</t>
+          <t>SWR-HWI-006</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4875,17 +4871,21 @@
           <t>RoverPlatformArch/.../rover_hardware_interface</t>
         </is>
       </c>
-      <c r="E125" s="3" t="n"/>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>rover_hardware_interface/test/domain/test_emergency_stop.cpp; rover_hardware_interface/test/rover_safety_controller/test_contact_coil_handler.cpp; rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp</t>
+        </is>
+      </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>tEStopLatch/testSwEStopZeroCommandIdealLink; tEStopLatch/testSwEStopZeroCommandWorstCaseLink</t>
+          <t>tEStopLatch/testSwEStopNeedsLatchReset</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-008</t>
+          <t>SWR-HWI-007</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-008</t>
+          <t>SYS-SR-007</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -4903,21 +4903,17 @@
           <t>RoverPlatformArch/.../rover_hardware_interface</t>
         </is>
       </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>rover_hardware_interface/test/rover_system/test_rover_system_write.cpp; rover_hardware_interface/test/domain/test_emergency_stop.cpp; rover_hardware_interface/test/domain/test_velocity_command_guard.cpp</t>
-        </is>
-      </c>
+      <c r="E126" s="3" t="n"/>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>tEStopLatch/testSwEStopNeedsLatchReset; tEStopLatch/testSwResetRefusedWhileMoving</t>
+          <t>tEStopLatch/testSwEStopZeroCommandIdealLink; tEStopLatch/testSwEStopZeroCommandWorstCaseLink</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-009</t>
+          <t>SWR-HWI-008</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4937,19 +4933,19 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/rover_safety_controller/test_contact_coil_handler.cpp; rover_hardware_interface/test/rover_safety_controller/test_safety_controller_adapters.cpp; rover_hardware_interface/test/domain/test_emergency_stop.cpp</t>
+          <t>rover_hardware_interface/test/rover_system/test_rover_system_write.cpp; rover_hardware_interface/test/domain/test_emergency_stop.cpp; rover_hardware_interface/test/domain/test_velocity_command_guard.cpp</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>tEStopLatch/testLatchHoldsAfterButtonRelease</t>
+          <t>tEStopLatch/testSwEStopNeedsLatchReset; tEStopLatch/testSwResetRefusedWhileMoving</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-010</t>
+          <t>SWR-HWI-009</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4967,17 +4963,21 @@
           <t>RoverPlatformArch/.../rover_hardware_interface</t>
         </is>
       </c>
-      <c r="E128" s="3" t="n"/>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>rover_hardware_interface/test/rover_safety_controller/test_contact_coil_handler.cpp; rover_hardware_interface/test/rover_safety_controller/test_safety_controller_adapters.cpp; rover_hardware_interface/test/domain/test_emergency_stop.cpp</t>
+        </is>
+      </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>tEStopLatch/testLatchResetRefusedWhileMoving</t>
+          <t>tEStopLatch/testLatchHoldsAfterButtonRelease</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-011</t>
+          <t>SWR-HWI-010</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-008, SYS-SR-024</t>
+          <t>SYS-SR-008</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -4995,21 +4995,17 @@
           <t>RoverPlatformArch/.../rover_hardware_interface</t>
         </is>
       </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>rover_hardware_interface/test/rover_safety_controller/test_contact_coil_handler.cpp; rover_hardware_interface/test/rover_safety_controller/test_safety_controller_adapters.cpp; rover_hardware_interface/test/domain/test_emergency_stop.cpp</t>
-        </is>
-      </c>
+      <c r="E129" s="3" t="n"/>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>tEStopLatch/testStartupLatched</t>
+          <t>tEStopLatch/testLatchResetRefusedWhileMoving</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-012</t>
+          <t>SWR-HWI-011</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -5019,7 +5015,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-006</t>
+          <t>SYS-SR-008, SYS-SR-024</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -5029,19 +5025,19 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/rover_safety_controller/test_contact_coil_handler.cpp</t>
+          <t>rover_hardware_interface/test/rover_safety_controller/test_contact_coil_handler.cpp; rover_hardware_interface/test/rover_safety_controller/test_safety_controller_adapters.cpp; rover_hardware_interface/test/domain/test_emergency_stop.cpp</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>tEStopLatch/testCpuWatchdogLossLatches</t>
+          <t>tEStopLatch/testStartupLatched</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-013</t>
+          <t>SWR-HWI-012</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -5051,7 +5047,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-023</t>
+          <t>SYS-SR-006</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -5061,15 +5057,19 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/rover_safety_controller/test_contact_coil_handler.cpp; rover_hardware_interface/test/rover_safety_controller/test_safety_controller_adapters.cpp; rover_hardware_interface/test/rover_system/test_rover_a1_system_on_init.cpp</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="n"/>
+          <t>rover_hardware_interface/test/rover_safety_controller/test_contact_coil_handler.cpp</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>tEStopLatch/testCpuWatchdogLossLatches</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-014</t>
+          <t>SWR-HWI-013</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp</t>
+          <t>rover_hardware_interface/test/rover_safety_controller/test_contact_coil_handler.cpp; rover_hardware_interface/test/rover_safety_controller/test_safety_controller_adapters.cpp; rover_hardware_interface/test/rover_system/test_rover_a1_system_on_init.cpp</t>
         </is>
       </c>
       <c r="F132" s="3" t="n"/>
@@ -5097,7 +5097,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-015</t>
+          <t>SWR-HWI-014</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-023, SYS-SR-022</t>
+          <t>SYS-SR-023</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp; rover_hardware_interface/test/rover_safety_controller/test_safety_controller_adapters.cpp</t>
+          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp</t>
         </is>
       </c>
       <c r="F133" s="3" t="n"/>
@@ -5125,7 +5125,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-016</t>
+          <t>SWR-HWI-015</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-023</t>
+          <t>SYS-SR-023, SYS-SR-022</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
@@ -5143,17 +5143,17 @@
           <t>RoverPlatformArch/.../rover_hardware_interface</t>
         </is>
       </c>
-      <c r="E134" s="3" t="n"/>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t>tEStopLatch/testEStopStatePublishLatency</t>
-        </is>
-      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp; rover_hardware_interface/test/rover_safety_controller/test_safety_controller_adapters.cpp</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-017</t>
+          <t>SWR-HWI-016</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-023, SYS-SR-022</t>
+          <t>SYS-SR-023</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -5172,12 +5172,16 @@
         </is>
       </c>
       <c r="E135" s="3" t="n"/>
-      <c r="F135" s="3" t="n"/>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>tEStopLatch/testEStopStatePublishLatency</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-018</t>
+          <t>SWR-HWI-017</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -5187,7 +5191,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-007, SYS-SR-008</t>
+          <t>SYS-SR-023, SYS-SR-022</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -5201,7 +5205,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-019</t>
+          <t>SWR-HWI-018</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -5211,7 +5215,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-006</t>
+          <t>SYS-SR-007, SYS-SR-008</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -5219,17 +5223,13 @@
           <t>RoverPlatformArch/.../rover_hardware_interface</t>
         </is>
       </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>rover_hardware_interface/test/domain/test_contactor_monitor.cpp; rover_hardware_interface/test/application/test_rover_control_loop_use_case.cpp; rover_hardware_interface/test/domain/test_safety_link_diagnosis.cpp</t>
-        </is>
-      </c>
+      <c r="E137" s="3" t="n"/>
       <c r="F137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-020</t>
+          <t>SWR-HWI-019</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-011</t>
+          <t>SYS-SR-006</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/rover_driver/test_phidget_motor_driver.cpp; rover_hardware_interface/test/application/test_rover_control_loop_use_case.cpp; rover_hardware_interface/test/domain/test_rover_error_filter.cpp; rover_hardware_interface/test/rover_system/test_rover_system_write.cpp</t>
+          <t>rover_hardware_interface/test/domain/test_contactor_monitor.cpp; rover_hardware_interface/test/application/test_rover_control_loop_use_case.cpp; rover_hardware_interface/test/domain/test_safety_link_diagnosis.cpp</t>
         </is>
       </c>
       <c r="F138" s="3" t="n"/>
@@ -5257,7 +5257,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-021</t>
+          <t>SWR-HWI-020</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-022</t>
+          <t>SYS-SR-011</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp; rover_hardware_interface/test/domain/test_driver_data_snapshot.cpp</t>
+          <t>rover_hardware_interface/test/rover_driver/test_phidget_motor_driver.cpp; rover_hardware_interface/test/application/test_rover_control_loop_use_case.cpp; rover_hardware_interface/test/domain/test_rover_error_filter.cpp; rover_hardware_interface/test/rover_system/test_rover_system_write.cpp</t>
         </is>
       </c>
       <c r="F139" s="3" t="n"/>
@@ -5285,7 +5285,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-022</t>
+          <t>SWR-HWI-021</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/domain/test_safety_link_diagnosis.cpp; rover_hardware_interface/test/rover_system/test_rover_system_write.cpp</t>
+          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp; rover_hardware_interface/test/domain/test_driver_data_snapshot.cpp</t>
         </is>
       </c>
       <c r="F140" s="3" t="n"/>
@@ -5313,7 +5313,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-023</t>
+          <t>SWR-HWI-022</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -5331,13 +5331,17 @@
           <t>RoverPlatformArch/.../rover_hardware_interface</t>
         </is>
       </c>
-      <c r="E141" s="3" t="n"/>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>rover_hardware_interface/test/domain/test_safety_link_diagnosis.cpp; rover_hardware_interface/test/rover_system/test_rover_system_write.cpp</t>
+        </is>
+      </c>
       <c r="F141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-024</t>
+          <t>SWR-HWI-023</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -5347,7 +5351,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-008, SYS-SR-022</t>
+          <t>SYS-SR-022</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -5361,7 +5365,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-025</t>
+          <t>SWR-HWI-024</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -5369,23 +5373,23 @@
           <t>rover_hardware_interface</t>
         </is>
       </c>
-      <c r="C143" s="3" t="n"/>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-008, SYS-SR-022</t>
+        </is>
+      </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_hardware_interface</t>
         </is>
       </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>rover_hardware_interface/test/rover_safety_controller/test_contact_coil_handler.cpp; rover_hardware_interface/test/rover_safety_controller/test_rover_safety_controller.cpp; rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp</t>
-        </is>
-      </c>
+      <c r="E143" s="3" t="n"/>
       <c r="F143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-026</t>
+          <t>SWR-HWI-025</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -5393,11 +5397,7 @@
           <t>rover_hardware_interface</t>
         </is>
       </c>
-      <c r="C144" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-019</t>
-        </is>
-      </c>
+      <c r="C144" s="3" t="n"/>
       <c r="D144" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_hardware_interface</t>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/rover_sensors/test_phidget_imu_sensor_on_init.cpp; rover_hardware_interface/test/domain/test_imu_calibration.cpp</t>
+          <t>rover_hardware_interface/test/rover_safety_controller/test_contact_coil_handler.cpp; rover_hardware_interface/test/rover_safety_controller/test_rover_safety_controller.cpp; rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp</t>
         </is>
       </c>
       <c r="F144" s="3" t="n"/>
@@ -5413,7 +5413,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-027</t>
+          <t>SWR-HWI-026</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-022</t>
+          <t>SYS-SR-019</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -5431,13 +5431,17 @@
           <t>RoverPlatformArch/.../rover_hardware_interface</t>
         </is>
       </c>
-      <c r="E145" s="3" t="n"/>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>rover_hardware_interface/test/rover_sensors/test_phidget_imu_sensor_on_init.cpp; rover_hardware_interface/test/domain/test_imu_calibration.cpp</t>
+        </is>
+      </c>
       <c r="F145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>SWR-HWI-028</t>
+          <t>SWR-HWI-027</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -5445,43 +5449,39 @@
           <t>rover_hardware_interface</t>
         </is>
       </c>
-      <c r="C146" s="3" t="n"/>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-022</t>
+        </is>
+      </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_hardware_interface</t>
         </is>
       </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>rover_hardware_interface/scripts/check_domain_purity.sh; rover_hardware_interface/scripts/check_application_purity.sh; rover_hardware_interface/scripts/check_rt_path_purity.sh</t>
-        </is>
-      </c>
+      <c r="E146" s="3" t="n"/>
       <c r="F146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-001</t>
+          <t>SWR-HWI-028</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>rover_led</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-009</t>
-        </is>
-      </c>
+          <t>rover_hardware_interface</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="n"/>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>RoverPlatformArch/.../rover_led</t>
+          <t>RoverPlatformArch/.../rover_hardware_interface</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/unit/domain/test_led_segment.cpp; rover_led/test/integration/test_led_controller_node.cpp</t>
+          <t>rover_hardware_interface/scripts/check_domain_purity.sh; rover_hardware_interface/scripts/check_application_purity.sh; rover_hardware_interface/scripts/check_rt_path_purity.sh</t>
         </is>
       </c>
       <c r="F147" s="3" t="n"/>
@@ -5489,7 +5489,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-002</t>
+          <t>SWR-LED-001</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/unit/domain/test_segment_layers.cpp; rover_led/test/unit/application/test_set_animation_use_case.cpp</t>
+          <t>rover_led/test/unit/domain/test_led_segment.cpp; rover_led/test/integration/test_led_controller_node.cpp</t>
         </is>
       </c>
       <c r="F148" s="3" t="n"/>
@@ -5517,7 +5517,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-003</t>
+          <t>SWR-LED-002</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/unit/application/test_set_animation_use_case.cpp; rover_led/test/integration/test_led_controller_node.cpp</t>
+          <t>rover_led/test/unit/domain/test_segment_layers.cpp; rover_led/test/unit/application/test_set_animation_use_case.cpp</t>
         </is>
       </c>
       <c r="F149" s="3" t="n"/>
@@ -5545,7 +5545,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-004</t>
+          <t>SWR-LED-003</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/unit/application/test_stop_animation_use_case.cpp; rover_led/test/unit/domain/test_segment_layers.cpp; rover_led/test/integration/test_led_controller_node.cpp</t>
+          <t>rover_led/test/unit/application/test_set_animation_use_case.cpp; rover_led/test/integration/test_led_controller_node.cpp</t>
         </is>
       </c>
       <c r="F150" s="3" t="n"/>
@@ -5573,7 +5573,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-005</t>
+          <t>SWR-LED-004</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/unit/application/test_render_tick_use_case.cpp; rover_led/test/integration/test_led_controller_node.cpp</t>
+          <t>rover_led/test/unit/application/test_stop_animation_use_case.cpp; rover_led/test/unit/domain/test_segment_layers.cpp; rover_led/test/integration/test_led_controller_node.cpp</t>
         </is>
       </c>
       <c r="F151" s="3" t="n"/>
@@ -5601,7 +5601,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-006</t>
+          <t>SWR-LED-005</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/unit/application/test_get_led_state_use_case.cpp; rover_led/test/integration/test_led_controller_node.cpp</t>
+          <t>rover_led/test/unit/application/test_render_tick_use_case.cpp; rover_led/test/integration/test_led_controller_node.cpp</t>
         </is>
       </c>
       <c r="F152" s="3" t="n"/>
@@ -5629,7 +5629,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-007</t>
+          <t>SWR-LED-006</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -5637,7 +5637,11 @@
           <t>rover_led</t>
         </is>
       </c>
-      <c r="C153" s="3" t="n"/>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-009</t>
+        </is>
+      </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_led</t>
@@ -5645,7 +5649,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/integration/test_led_controller_node.cpp</t>
+          <t>rover_led/test/unit/application/test_get_led_state_use_case.cpp; rover_led/test/integration/test_led_controller_node.cpp</t>
         </is>
       </c>
       <c r="F153" s="3" t="n"/>
@@ -5653,7 +5657,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-008</t>
+          <t>SWR-LED-007</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -5667,13 +5671,17 @@
           <t>RoverPlatformArch/.../rover_led</t>
         </is>
       </c>
-      <c r="E154" s="3" t="n"/>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>rover_led/test/integration/test_led_controller_node.cpp</t>
+        </is>
+      </c>
       <c r="F154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-009</t>
+          <t>SWR-LED-008</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -5681,27 +5689,19 @@
           <t>rover_led</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-009</t>
-        </is>
-      </c>
+      <c r="C155" s="3" t="n"/>
       <c r="D155" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_led</t>
         </is>
       </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>rover_led/test/unit/infrastructure/test_yaml_led_config.cpp; rover_led/test/unit/infrastructure/test_shipped_blinkers.cpp</t>
-        </is>
-      </c>
+      <c r="E155" s="3" t="n"/>
       <c r="F155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-010</t>
+          <t>SWR-LED-009</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-009, SYS-SR-010</t>
+          <t>SYS-SR-009</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -5721,19 +5721,15 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/unit/infrastructure/test_yaml_led_config.cpp</t>
-        </is>
-      </c>
-      <c r="F156" s="3" t="inlineStr">
-        <is>
-          <t>tPlatformModeManager/testLedMapping</t>
-        </is>
-      </c>
+          <t>rover_led/test/unit/infrastructure/test_yaml_led_config.cpp; rover_led/test/unit/infrastructure/test_shipped_blinkers.cpp</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-011</t>
+          <t>SWR-LED-010</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5743,7 +5739,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-009</t>
+          <t>SYS-SR-009, SYS-SR-010</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -5753,15 +5749,19 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/unit/domain/test_sk9822_frame_encoder.cpp; rover_led/test/unit/application/test_encode_frame_use_case.cpp</t>
-        </is>
-      </c>
-      <c r="F157" s="3" t="n"/>
+          <t>rover_led/test/unit/infrastructure/test_yaml_led_config.cpp</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>tPlatformModeManager/testLedMapping</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-012</t>
+          <t>SWR-LED-011</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/unit/application/test_encode_frame_use_case.cpp; rover_led/test/integration/test_led_driver_node.cpp</t>
+          <t>rover_led/test/unit/domain/test_sk9822_frame_encoder.cpp; rover_led/test/unit/application/test_encode_frame_use_case.cpp</t>
         </is>
       </c>
       <c r="F158" s="3" t="n"/>
@@ -5789,7 +5789,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-013</t>
+          <t>SWR-LED-012</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/integration/test_led_driver_node.cpp</t>
+          <t>rover_led/test/unit/application/test_encode_frame_use_case.cpp; rover_led/test/integration/test_led_driver_node.cpp</t>
         </is>
       </c>
       <c r="F159" s="3" t="n"/>
@@ -5817,7 +5817,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-014</t>
+          <t>SWR-LED-013</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/unit/application/test_set_brightness_use_case.cpp; rover_led/test/integration/test_led_driver_node.cpp</t>
+          <t>rover_led/test/integration/test_led_driver_node.cpp</t>
         </is>
       </c>
       <c r="F160" s="3" t="n"/>
@@ -5845,7 +5845,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-015</t>
+          <t>SWR-LED-014</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-009, SYS-SR-024</t>
+          <t>SYS-SR-009</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/integration/test_led_driver_node.cpp</t>
+          <t>rover_led/test/unit/application/test_set_brightness_use_case.cpp; rover_led/test/integration/test_led_driver_node.cpp</t>
         </is>
       </c>
       <c r="F161" s="3" t="n"/>
@@ -5873,7 +5873,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-016</t>
+          <t>SWR-LED-015</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5881,7 +5881,11 @@
           <t>rover_led</t>
         </is>
       </c>
-      <c r="C162" s="3" t="n"/>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-009, SYS-SR-024</t>
+        </is>
+      </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_led</t>
@@ -5889,7 +5893,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/unit/application/test_led_control_handshake.cpp; rover_led/test/integration/test_led_driver_node.cpp</t>
+          <t>rover_led/test/integration/test_led_driver_node.cpp</t>
         </is>
       </c>
       <c r="F162" s="3" t="n"/>
@@ -5897,7 +5901,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-017</t>
+          <t>SWR-LED-016</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5905,11 +5909,7 @@
           <t>rover_led</t>
         </is>
       </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-022</t>
-        </is>
-      </c>
+      <c r="C163" s="3" t="n"/>
       <c r="D163" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_led</t>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/unit/infrastructure/test_led_controller_diagnostics.cpp; rover_led/test/integration/test_led_controller_node.cpp</t>
+          <t>rover_led/test/unit/application/test_led_control_handshake.cpp; rover_led/test/integration/test_led_driver_node.cpp</t>
         </is>
       </c>
       <c r="F163" s="3" t="n"/>
@@ -5925,7 +5925,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-018</t>
+          <t>SWR-LED-017</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5943,13 +5943,17 @@
           <t>RoverPlatformArch/.../rover_led</t>
         </is>
       </c>
-      <c r="E164" s="3" t="n"/>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>rover_led/test/unit/infrastructure/test_led_controller_diagnostics.cpp; rover_led/test/integration/test_led_controller_node.cpp</t>
+        </is>
+      </c>
       <c r="F164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-019</t>
+          <t>SWR-LED-018</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5959,7 +5963,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-009, SYS-SR-024</t>
+          <t>SYS-SR-022</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -5967,17 +5971,13 @@
           <t>RoverPlatformArch/.../rover_led</t>
         </is>
       </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>rover_led/test/test_launch_structure.py</t>
-        </is>
-      </c>
+      <c r="E165" s="3" t="n"/>
       <c r="F165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-020</t>
+          <t>SWR-LED-019</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-009, SYS-SR-010</t>
+          <t>SYS-SR-009, SYS-SR-024</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -5995,17 +5995,17 @@
           <t>RoverPlatformArch/.../rover_led</t>
         </is>
       </c>
-      <c r="E166" s="3" t="n"/>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t>tPlatformModeManager/testLedDefinedForEveryState</t>
-        </is>
-      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>rover_led/test/test_launch_structure.py</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>SWR-LED-021</t>
+          <t>SWR-LED-020</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -6024,27 +6024,31 @@
         </is>
       </c>
       <c r="E167" s="3" t="n"/>
-      <c r="F167" s="3" t="n"/>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>tPlatformModeManager/testLedDefinedForEveryState</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-001</t>
+          <t>SWR-LED-021</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>rover_localization</t>
+          <t>rover_led</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-003</t>
+          <t>SYS-SR-009, SYS-SR-010</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>RoverPlatformArch/.../rover_localization</t>
+          <t>RoverPlatformArch/.../rover_led</t>
         </is>
       </c>
       <c r="E168" s="3" t="n"/>
@@ -6053,7 +6057,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-002</t>
+          <t>SWR-LOC-001</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -6077,7 +6081,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-003</t>
+          <t>SWR-LOC-002</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -6101,7 +6105,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-004</t>
+          <t>SWR-LOC-003</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -6111,7 +6115,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-003, SYS-SR-019</t>
+          <t>SYS-SR-003</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -6125,7 +6129,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-005</t>
+          <t>SWR-LOC-004</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -6135,7 +6139,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-003, SYS-SR-021</t>
+          <t>SYS-SR-003, SYS-SR-019</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -6149,7 +6153,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-006</t>
+          <t>SWR-LOC-005</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -6159,7 +6163,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-021</t>
+          <t>SYS-SR-003, SYS-SR-021</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -6173,7 +6177,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-007</t>
+          <t>SWR-LOC-006</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -6181,7 +6185,11 @@
           <t>rover_localization</t>
         </is>
       </c>
-      <c r="C174" s="3" t="n"/>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-021</t>
+        </is>
+      </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_localization</t>
@@ -6193,7 +6201,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-008</t>
+          <t>SWR-LOC-007</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -6201,11 +6209,7 @@
           <t>rover_localization</t>
         </is>
       </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-022</t>
-        </is>
-      </c>
+      <c r="C175" s="3" t="n"/>
       <c r="D175" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_localization</t>
@@ -6217,7 +6221,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-009</t>
+          <t>SWR-LOC-008</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -6227,7 +6231,7 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-021</t>
+          <t>SYS-SR-022</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -6241,7 +6245,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-010</t>
+          <t>SWR-LOC-009</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -6265,7 +6269,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-011</t>
+          <t>SWR-LOC-010</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -6289,7 +6293,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-012</t>
+          <t>SWR-LOC-011</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -6313,7 +6317,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-013</t>
+          <t>SWR-LOC-012</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -6321,7 +6325,11 @@
           <t>rover_localization</t>
         </is>
       </c>
-      <c r="C180" s="3" t="n"/>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-021</t>
+        </is>
+      </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_localization</t>
@@ -6333,7 +6341,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-014</t>
+          <t>SWR-LOC-013</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -6353,7 +6361,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-015</t>
+          <t>SWR-LOC-014</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -6373,7 +6381,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>SWR-LOC-016</t>
+          <t>SWR-LOC-015</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -6381,11 +6389,7 @@
           <t>rover_localization</t>
         </is>
       </c>
-      <c r="C183" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-003, SYS-SR-021</t>
-        </is>
-      </c>
+      <c r="C183" s="3" t="n"/>
       <c r="D183" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_localization</t>
@@ -6397,35 +6401,31 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>SWR-MSG-001</t>
+          <t>SWR-LOC-016</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>rover_msgs</t>
+          <t>rover_localization</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-023</t>
+          <t>SYS-SR-003, SYS-SR-021</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>RoverPlatformArch/.../rover_msgs</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="inlineStr">
-        <is>
-          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp; rover_twist_mux/test/integration/test_motion_lock_node.cpp</t>
-        </is>
-      </c>
+          <t>RoverPlatformArch/.../rover_localization</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="n"/>
       <c r="F184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>SWR-MSG-002</t>
+          <t>SWR-MSG-001</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-023, SYS-SR-022</t>
+          <t>SYS-SR-023</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -6453,7 +6453,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>SWR-MSG-003</t>
+          <t>SWR-MSG-002</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-023</t>
+          <t>SYS-SR-023, SYS-SR-022</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp</t>
+          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp; rover_twist_mux/test/integration/test_motion_lock_node.cpp</t>
         </is>
       </c>
       <c r="F186" s="3" t="n"/>
@@ -6481,7 +6481,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>SWR-MSG-004</t>
+          <t>SWR-MSG-003</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-023, SYS-SR-022</t>
+          <t>SYS-SR-023</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -6499,13 +6499,17 @@
           <t>RoverPlatformArch/.../rover_msgs</t>
         </is>
       </c>
-      <c r="E187" s="3" t="n"/>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp</t>
+        </is>
+      </c>
       <c r="F187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>SWR-MSG-005</t>
+          <t>SWR-MSG-004</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6515,7 +6519,7 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-023</t>
+          <t>SYS-SR-023, SYS-SR-022</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -6523,17 +6527,13 @@
           <t>RoverPlatformArch/.../rover_msgs</t>
         </is>
       </c>
-      <c r="E188" s="3" t="inlineStr">
-        <is>
-          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp; rover_twist_mux/test/integration/test_motion_lock_node.cpp</t>
-        </is>
-      </c>
+      <c r="E188" s="3" t="n"/>
       <c r="F188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>SWR-MSG-006</t>
+          <t>SWR-MSG-005</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-007</t>
+          <t>SYS-SR-023</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -6551,13 +6551,17 @@
           <t>RoverPlatformArch/.../rover_msgs</t>
         </is>
       </c>
-      <c r="E189" s="3" t="n"/>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp; rover_twist_mux/test/integration/test_motion_lock_node.cpp</t>
+        </is>
+      </c>
       <c r="F189" s="3" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>SWR-MSG-007</t>
+          <t>SWR-MSG-006</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -6565,23 +6569,23 @@
           <t>rover_msgs</t>
         </is>
       </c>
-      <c r="C190" s="3" t="n"/>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-007</t>
+        </is>
+      </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_msgs</t>
         </is>
       </c>
-      <c r="E190" s="3" t="inlineStr">
-        <is>
-          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp</t>
-        </is>
-      </c>
+      <c r="E190" s="3" t="n"/>
       <c r="F190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>SWR-MSG-008</t>
+          <t>SWR-MSG-007</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -6589,11 +6593,7 @@
           <t>rover_msgs</t>
         </is>
       </c>
-      <c r="C191" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-022</t>
-        </is>
-      </c>
+      <c r="C191" s="3" t="n"/>
       <c r="D191" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_msgs</t>
@@ -6609,7 +6609,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>SWR-MSG-009</t>
+          <t>SWR-MSG-008</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-012</t>
+          <t>SYS-SR-022</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>rover_crsf_teleop/test/unit/test_rc_message_conversions.cpp</t>
+          <t>rover_hardware_interface/test/system_ros_interface/test_system_ros_interface.cpp</t>
         </is>
       </c>
       <c r="F192" s="3" t="n"/>
@@ -6637,7 +6637,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>SWR-MSG-010</t>
+          <t>SWR-MSG-009</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-009, SYS-SR-010</t>
+          <t>SYS-SR-012</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -6655,17 +6655,17 @@
           <t>RoverPlatformArch/.../rover_msgs</t>
         </is>
       </c>
-      <c r="E193" s="3" t="n"/>
-      <c r="F193" s="3" t="inlineStr">
-        <is>
-          <t>tPlatformModeManager/testLedDefinedForEveryState</t>
-        </is>
-      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>rover_crsf_teleop/test/unit/test_rc_message_conversions.cpp</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>SWR-MSG-011</t>
+          <t>SWR-MSG-010</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-010</t>
+          <t>SYS-SR-009, SYS-SR-010</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -6684,12 +6684,16 @@
         </is>
       </c>
       <c r="E194" s="3" t="n"/>
-      <c r="F194" s="3" t="n"/>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>tPlatformModeManager/testLedDefinedForEveryState</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>SWR-MSG-012</t>
+          <t>SWR-MSG-011</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -6699,7 +6703,7 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-020</t>
+          <t>SYS-SR-010</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -6713,22 +6717,22 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-001</t>
+          <t>SWR-MSG-012</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>rover_safety</t>
+          <t>rover_msgs</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-007, SYS-SR-016</t>
+          <t>SYS-SR-020</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>RoverPlatformArch/.../rover_safety</t>
+          <t>RoverPlatformArch/.../rover_msgs</t>
         </is>
       </c>
       <c r="E196" s="3" t="n"/>
@@ -6737,7 +6741,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-002</t>
+          <t>SWR-SAF-001</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -6747,7 +6751,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-017, SYS-SR-007</t>
+          <t>SYS-SR-007, SYS-SR-016</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -6755,17 +6759,13 @@
           <t>RoverPlatformArch/.../rover_safety</t>
         </is>
       </c>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>rover_safety/test/unit/test_battery_safety_policy.cpp</t>
-        </is>
-      </c>
+      <c r="E197" s="3" t="n"/>
       <c r="F197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-003</t>
+          <t>SWR-SAF-002</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -6773,7 +6773,11 @@
           <t>rover_safety</t>
         </is>
       </c>
-      <c r="C198" s="3" t="n"/>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-017, SYS-SR-007</t>
+        </is>
+      </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_safety</t>
@@ -6781,7 +6785,7 @@
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>rover_safety/test/unit/test_battery_safety_policy.cpp; rover_safety/test/integration/test_safety_node_shutdown.cpp</t>
+          <t>rover_safety/test/unit/test_battery_safety_policy.cpp</t>
         </is>
       </c>
       <c r="F198" s="3" t="n"/>
@@ -6789,7 +6793,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-004</t>
+          <t>SWR-SAF-003</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -6805,7 +6809,7 @@
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>rover_safety/test/unit/test_battery_safety_policy.cpp</t>
+          <t>rover_safety/test/unit/test_battery_safety_policy.cpp; rover_safety/test/integration/test_safety_node_shutdown.cpp</t>
         </is>
       </c>
       <c r="F199" s="3" t="n"/>
@@ -6813,7 +6817,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-005</t>
+          <t>SWR-SAF-004</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -6821,11 +6825,7 @@
           <t>rover_safety</t>
         </is>
       </c>
-      <c r="C200" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-007, SYS-SR-017</t>
-        </is>
-      </c>
+      <c r="C200" s="3" t="n"/>
       <c r="D200" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_safety</t>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>rover_safety/test/integration/test_safety_node_shutdown.cpp; rover_safety/test/integration/test_call_trigger_service.cpp</t>
+          <t>rover_safety/test/unit/test_battery_safety_policy.cpp</t>
         </is>
       </c>
       <c r="F200" s="3" t="n"/>
@@ -6841,7 +6841,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-006</t>
+          <t>SWR-SAF-005</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-017</t>
+          <t>SYS-SR-007, SYS-SR-017</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -6859,13 +6859,17 @@
           <t>RoverPlatformArch/.../rover_safety</t>
         </is>
       </c>
-      <c r="E201" s="3" t="n"/>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>rover_safety/test/integration/test_safety_node_shutdown.cpp; rover_safety/test/integration/test_call_trigger_service.cpp</t>
+        </is>
+      </c>
       <c r="F201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-007</t>
+          <t>SWR-SAF-006</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -6873,23 +6877,23 @@
           <t>rover_safety</t>
         </is>
       </c>
-      <c r="C202" s="3" t="n"/>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-017</t>
+        </is>
+      </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_safety</t>
         </is>
       </c>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>rover_safety/test/integration/test_shutdown_tree.cpp; rover_safety/test/integration/test_safety_node_shutdown.cpp; rover_safety/test/integration/test_shutdown_script.sh; rover_safety/test/unit/plugins/test_execute_command_node.cpp; rover_safety/test/unit/plugins/test_shutdown_hosts_from_file_node.cpp</t>
-        </is>
-      </c>
+      <c r="E202" s="3" t="n"/>
       <c r="F202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-008</t>
+          <t>SWR-SAF-007</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -6905,7 +6909,7 @@
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>rover_safety/test/unit/test_shutdown_sequence.cpp; rover_safety/test/integration/test_safety_node_shutdown.cpp</t>
+          <t>rover_safety/test/integration/test_shutdown_tree.cpp; rover_safety/test/integration/test_safety_node_shutdown.cpp; rover_safety/test/integration/test_shutdown_script.sh; rover_safety/test/unit/plugins/test_execute_command_node.cpp; rover_safety/test/unit/plugins/test_shutdown_hosts_from_file_node.cpp</t>
         </is>
       </c>
       <c r="F203" s="3" t="n"/>
@@ -6913,7 +6917,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-009</t>
+          <t>SWR-SAF-008</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -6921,11 +6925,7 @@
           <t>rover_safety</t>
         </is>
       </c>
-      <c r="C204" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-022</t>
-        </is>
-      </c>
+      <c r="C204" s="3" t="n"/>
       <c r="D204" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_safety</t>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>rover_safety/test/unit/test_safety_health.cpp; rover_safety/test/unit/test_safety_diagnostics.cpp</t>
+          <t>rover_safety/test/unit/test_shutdown_sequence.cpp; rover_safety/test/integration/test_safety_node_shutdown.cpp</t>
         </is>
       </c>
       <c r="F204" s="3" t="n"/>
@@ -6941,7 +6941,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-010</t>
+          <t>SWR-SAF-009</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-024</t>
+          <t>SYS-SR-022</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>rover_safety/test/integration/test_led_safety_configure_retry.cpp</t>
+          <t>rover_safety/test/unit/test_safety_health.cpp; rover_safety/test/unit/test_safety_diagnostics.cpp</t>
         </is>
       </c>
       <c r="F205" s="3" t="n"/>
@@ -6969,7 +6969,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-011</t>
+          <t>SWR-SAF-010</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6977,19 +6977,27 @@
           <t>rover_safety</t>
         </is>
       </c>
-      <c r="C206" s="3" t="n"/>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-024</t>
+        </is>
+      </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_safety</t>
         </is>
       </c>
-      <c r="E206" s="3" t="n"/>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>rover_safety/test/integration/test_led_safety_configure_retry.cpp</t>
+        </is>
+      </c>
       <c r="F206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-012</t>
+          <t>SWR-SAF-011</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6997,11 +7005,7 @@
           <t>rover_safety</t>
         </is>
       </c>
-      <c r="C207" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-022</t>
-        </is>
-      </c>
+      <c r="C207" s="3" t="n"/>
       <c r="D207" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_safety</t>
@@ -7013,7 +7017,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-013</t>
+          <t>SWR-SAF-012</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -7023,7 +7027,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-009</t>
+          <t>SYS-SR-022</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -7031,17 +7035,13 @@
           <t>RoverPlatformArch/.../rover_safety</t>
         </is>
       </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>rover_safety/test/integration/test_led_safety_node_animations.cpp; rover_safety/test/unit/test_led_safety_tree.cpp</t>
-        </is>
-      </c>
+      <c r="E208" s="3" t="n"/>
       <c r="F208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-014</t>
+          <t>SWR-SAF-013</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>rover_safety/test/unit/test_led_animation_policy.cpp; rover_safety/test/integration/test_led_safety_node_animations.cpp</t>
+          <t>rover_safety/test/integration/test_led_safety_node_animations.cpp; rover_safety/test/unit/test_led_safety_tree.cpp</t>
         </is>
       </c>
       <c r="F209" s="3" t="n"/>
@@ -7069,7 +7069,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-015</t>
+          <t>SWR-SAF-014</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>rover_safety/test/unit/test_led_animation_policy.cpp; rover_safety/test/unit/test_led_safety_tree.cpp</t>
+          <t>rover_safety/test/unit/test_led_animation_policy.cpp; rover_safety/test/integration/test_led_safety_node_animations.cpp</t>
         </is>
       </c>
       <c r="F210" s="3" t="n"/>
@@ -7097,7 +7097,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-016</t>
+          <t>SWR-SAF-015</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>rover_safety/test/unit/test_led_animation_policy.cpp</t>
+          <t>rover_safety/test/unit/test_led_animation_policy.cpp; rover_safety/test/unit/test_led_safety_tree.cpp</t>
         </is>
       </c>
       <c r="F211" s="3" t="n"/>
@@ -7125,7 +7125,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-017</t>
+          <t>SWR-SAF-016</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-022</t>
+          <t>SYS-SR-009</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>rover_safety/test/unit/test_safety_diagnostics.cpp; rover_safety/test/unit/test_safety_health.cpp</t>
+          <t>rover_safety/test/unit/test_led_animation_policy.cpp</t>
         </is>
       </c>
       <c r="F212" s="3" t="n"/>
@@ -7153,7 +7153,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-018</t>
+          <t>SWR-SAF-017</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-010</t>
+          <t>SYS-SR-022</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -7171,17 +7171,17 @@
           <t>RoverPlatformArch/.../rover_safety</t>
         </is>
       </c>
-      <c r="E213" s="3" t="n"/>
-      <c r="F213" s="3" t="inlineStr">
-        <is>
-          <t>tPlatformModeManager/testEveryStateReachable; tPlatformModeManager/testNoMotionOutsideOperationalStates</t>
-        </is>
-      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>rover_safety/test/unit/test_safety_diagnostics.cpp; rover_safety/test/unit/test_safety_health.cpp</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-019</t>
+          <t>SWR-SAF-018</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-010, SYS-SR-008, SYS-SR-024</t>
+          <t>SYS-SR-010</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -7202,14 +7202,14 @@
       <c r="E214" s="3" t="n"/>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>tPlatformModeManager/testEveryStateReachable; tPlatformModeManager/testTeleopAutonomousFollowActiveSource; tPlatformModeManager/testEStopHasPriorityAndNeedsClear</t>
+          <t>tPlatformModeManager/testEveryStateReachable; tPlatformModeManager/testNoMotionOutsideOperationalStates</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-020</t>
+          <t>SWR-SAF-019</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-017, SYS-SR-010</t>
+          <t>SYS-SR-010, SYS-SR-008, SYS-SR-024</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -7230,14 +7230,14 @@
       <c r="E215" s="3" t="n"/>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>tPlatformModeManager/testLowBatteryWarningAndSafeStop</t>
+          <t>tPlatformModeManager/testEveryStateReachable; tPlatformModeManager/testTeleopAutonomousFollowActiveSource; tPlatformModeManager/testEStopHasPriorityAndNeedsClear</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-021</t>
+          <t>SWR-SAF-020</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-010, SYS-SR-022</t>
+          <t>SYS-SR-017, SYS-SR-010</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -7258,14 +7258,14 @@
       <c r="E216" s="3" t="n"/>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>tPlatformModeManager/testFaultNeedsReset</t>
+          <t>tPlatformModeManager/testLowBatteryWarningAndSafeStop</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>SWR-SAF-022</t>
+          <t>SWR-SAF-021</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-009, SYS-SR-010</t>
+          <t>SYS-SR-010, SYS-SR-022</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -7286,42 +7286,42 @@
       <c r="E217" s="3" t="n"/>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>tPlatformModeManager/testLedMapping</t>
+          <t>tPlatformModeManager/testFaultNeedsReset</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-001</t>
+          <t>SWR-SAF-022</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>rover_transport</t>
+          <t>rover_safety</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-005</t>
+          <t>SYS-SR-009, SYS-SR-010</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>RoverPlatformArch/.../rover_transport</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>rover_transport/rover_serial_driver/test/integration/test_serial_bridge_node_lifecycle.cpp; rover_transport/rover_serial_driver/test/unit/test_serial_msg_conversions.cpp; rover_transport/rover_io_context/test/unit/test_byte_bridges.cpp</t>
-        </is>
-      </c>
-      <c r="F218" s="3" t="n"/>
+          <t>RoverPlatformArch/.../rover_safety</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="n"/>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>tPlatformModeManager/testLedMapping</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-002</t>
+          <t>SWR-TRN-004</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -7329,11 +7329,7 @@
           <t>rover_transport</t>
         </is>
       </c>
-      <c r="C219" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-005</t>
-        </is>
-      </c>
+      <c r="C219" s="3" t="n"/>
       <c r="D219" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_transport</t>
@@ -7341,7 +7337,7 @@
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>rover_transport/rover_serial_driver/test/integration/test_serial_bridge_node_lifecycle.cpp</t>
+          <t>rover_transport/rover_udp_driver/test/integration/test_udp_nodes_lifecycle.cpp</t>
         </is>
       </c>
       <c r="F219" s="3" t="n"/>
@@ -7349,7 +7345,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-003</t>
+          <t>SWR-TRN-005</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -7357,23 +7353,23 @@
           <t>rover_transport</t>
         </is>
       </c>
-      <c r="C220" s="3" t="n"/>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-024</t>
+        </is>
+      </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_transport</t>
         </is>
       </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>rover_transport/rover_serial_driver/test/unit/test_serial_port_config.cpp; rover_transport/rover_serial_driver/test/unit/test_asio_serial_options.cpp; rover_transport/rover_serial_driver/test/integration/test_serial_bridge_node_lifecycle.cpp</t>
-        </is>
-      </c>
+      <c r="E220" s="3" t="n"/>
       <c r="F220" s="3" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-004</t>
+          <t>SWR-TRN-006</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -7381,7 +7377,11 @@
           <t>rover_transport</t>
         </is>
       </c>
-      <c r="C221" s="3" t="n"/>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-005, SYS-SR-016</t>
+        </is>
+      </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_transport</t>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>rover_transport/rover_serial_driver/test/integration/test_serial_bridge_node_lifecycle.cpp; rover_transport/rover_udp_driver/test/integration/test_udp_nodes_lifecycle.cpp</t>
+          <t>rover_transport/rover_udp_driver/test/integration/test_udp_nodes_lifecycle.cpp; rover_transport/rover_udp_driver/test/integration/test_asio_udp_socket.cpp; rover_transport/rover_udp_driver/test/unit/test_udp_packet_conversions.cpp; rover_crsf_teleop/test/e2e/test_teleop_launch.py</t>
         </is>
       </c>
       <c r="F221" s="3" t="n"/>
@@ -7397,7 +7397,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-005</t>
+          <t>SWR-TRN-007</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-024</t>
+          <t>SYS-SR-016</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-006</t>
+          <t>SWR-TRN-008</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-016</t>
+          <t>SYS-SR-005, SYS-SR-016, SYS-SR-022</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -7439,17 +7439,13 @@
           <t>RoverPlatformArch/.../rover_transport</t>
         </is>
       </c>
-      <c r="E223" s="3" t="inlineStr">
-        <is>
-          <t>rover_transport/rover_udp_driver/test/integration/test_udp_nodes_lifecycle.cpp; rover_transport/rover_udp_driver/test/integration/test_asio_udp_socket.cpp; rover_transport/rover_udp_driver/test/unit/test_udp_packet_conversions.cpp</t>
-        </is>
-      </c>
+      <c r="E223" s="3" t="n"/>
       <c r="F223" s="3" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-007</t>
+          <t>SWR-TRN-009</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -7459,7 +7455,7 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-016</t>
+          <t>SYS-SR-009</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -7467,13 +7463,17 @@
           <t>RoverPlatformArch/.../rover_transport</t>
         </is>
       </c>
-      <c r="E224" s="3" t="n"/>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>rover_transport/rover_udp_driver/test/integration/test_udp_nodes_lifecycle.cpp; rover_transport/rover_udp_driver/test/integration/test_asio_udp_socket.cpp; rover_led/test/test_launch_structure.py</t>
+        </is>
+      </c>
       <c r="F224" s="3" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-008</t>
+          <t>SWR-TRN-010</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -7481,23 +7481,23 @@
           <t>rover_transport</t>
         </is>
       </c>
-      <c r="C225" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-005, SYS-SR-016, SYS-SR-022</t>
-        </is>
-      </c>
+      <c r="C225" s="3" t="n"/>
       <c r="D225" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_transport</t>
         </is>
       </c>
-      <c r="E225" s="3" t="n"/>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>rover_transport/rover_udp_driver/test/unit/test_udp_endpoint.cpp; rover_transport/rover_udp_driver/test/integration/test_udp_nodes_lifecycle.cpp</t>
+        </is>
+      </c>
       <c r="F225" s="3" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-009</t>
+          <t>SWR-TRN-011</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -7505,11 +7505,7 @@
           <t>rover_transport</t>
         </is>
       </c>
-      <c r="C226" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-009</t>
-        </is>
-      </c>
+      <c r="C226" s="3" t="n"/>
       <c r="D226" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_transport</t>
@@ -7517,7 +7513,7 @@
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>rover_transport/rover_udp_driver/test/integration/test_udp_nodes_lifecycle.cpp; rover_transport/rover_udp_driver/test/integration/test_asio_udp_socket.cpp; rover_led/test/test_launch_structure.py</t>
+          <t>rover_transport/rover_io_context/test/unit/test_byte_bridges.cpp</t>
         </is>
       </c>
       <c r="F226" s="3" t="n"/>
@@ -7525,7 +7521,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-010</t>
+          <t>SWR-TRN-012</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7541,7 +7537,7 @@
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>rover_transport/rover_udp_driver/test/unit/test_udp_endpoint.cpp; rover_transport/rover_udp_driver/test/integration/test_udp_nodes_lifecycle.cpp</t>
+          <t>rover_transport/rover_udp_driver/test/unit/test_udp_packet_conversions.cpp</t>
         </is>
       </c>
       <c r="F227" s="3" t="n"/>
@@ -7549,7 +7545,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-011</t>
+          <t>SWR-TRN-013</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7565,7 +7561,7 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>rover_transport/rover_io_context/test/unit/test_byte_bridges.cpp</t>
+          <t>rover_transport/rover_io_context/test/unit/test_async_op_guard.cpp; rover_transport/rover_udp_driver/test/integration/test_udp_nodes_lifecycle.cpp</t>
         </is>
       </c>
       <c r="F228" s="3" t="n"/>
@@ -7573,7 +7569,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-012</t>
+          <t>SWR-TRN-014</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7589,7 +7585,7 @@
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>rover_transport/rover_serial_driver/test/unit/test_serial_msg_conversions.cpp; rover_transport/rover_udp_driver/test/unit/test_udp_packet_conversions.cpp</t>
+          <t>rover_led/test/test_launch_structure.py; rover_crsf_teleop/test/test_launch_structure.py</t>
         </is>
       </c>
       <c r="F229" s="3" t="n"/>
@@ -7597,7 +7593,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-013</t>
+          <t>SWR-TRN-015</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7605,7 +7601,11 @@
           <t>rover_transport</t>
         </is>
       </c>
-      <c r="C230" s="3" t="n"/>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-006, SYS-SR-007, SYS-SR-023</t>
+        </is>
+      </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_transport</t>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>rover_transport/rover_io_context/test/unit/test_async_op_guard.cpp; rover_transport/rover_serial_driver/test/integration/test_serial_bridge_node_lifecycle.cpp; rover_transport/rover_udp_driver/test/integration/test_udp_nodes_lifecycle.cpp</t>
+          <t>rover_transport/rover_modbus_driver/test/unit/test_modbus_discrete_io_client.cpp; rover_transport/rover_modbus_driver/test/unit/test_mb_frame_mapping.cpp; rover_transport/rover_modbus_driver/test/e2e/test_modbus_tcp_roundtrip.cpp; rover_transport/rover_modbus_driver/test/e2e/test_modbus_tcp_reply_handling.cpp</t>
         </is>
       </c>
       <c r="F230" s="3" t="n"/>
@@ -7621,7 +7621,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-014</t>
+          <t>SWR-TRN-016</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7629,7 +7629,11 @@
           <t>rover_transport</t>
         </is>
       </c>
-      <c r="C231" s="3" t="n"/>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-006, SYS-SR-008</t>
+        </is>
+      </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_transport</t>
@@ -7637,7 +7641,7 @@
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>rover_led/test/test_launch_structure.py</t>
+          <t>rover_transport/rover_modbus_driver/test/unit/test_modbus_discrete_io_client.cpp; rover_transport/rover_modbus_driver/test/unit/test_modbus_discrete_io_client_failures.cpp</t>
         </is>
       </c>
       <c r="F231" s="3" t="n"/>
@@ -7645,7 +7649,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-015</t>
+          <t>SWR-TRN-017</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -7655,7 +7659,7 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-006, SYS-SR-007, SYS-SR-023</t>
+          <t>SYS-SR-006, SYS-SR-024</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -7665,7 +7669,7 @@
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>rover_transport/rover_modbus_driver/test/unit/test_modbus_discrete_io_client.cpp; rover_transport/rover_modbus_driver/test/unit/test_mb_frame_mapping.cpp; rover_transport/rover_modbus_driver/test/e2e/test_modbus_tcp_roundtrip.cpp; rover_transport/rover_modbus_driver/test/e2e/test_modbus_tcp_reply_handling.cpp</t>
+          <t>rover_transport/rover_modbus_driver/test/unit/test_modbus_discrete_io_client.cpp; rover_transport/rover_modbus_driver/test/integration/test_modbus_tcp_transport.cpp</t>
         </is>
       </c>
       <c r="F232" s="3" t="n"/>
@@ -7673,7 +7677,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-016</t>
+          <t>SWR-TRN-018</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -7683,7 +7687,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-006, SYS-SR-008</t>
+          <t>SYS-SR-007, SYS-SR-023</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -7693,7 +7697,7 @@
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>rover_transport/rover_modbus_driver/test/unit/test_modbus_discrete_io_client.cpp; rover_transport/rover_modbus_driver/test/unit/test_modbus_discrete_io_client_failures.cpp</t>
+          <t>rover_transport/rover_modbus_driver/test/unit/test_modbus_discrete_io_client.cpp; rover_transport/rover_modbus_driver/test/unit/test_modbus_discrete_io_client_failures.cpp; rover_transport/rover_modbus_driver/test/e2e/test_modbus_tcp_reply_handling.cpp</t>
         </is>
       </c>
       <c r="F233" s="3" t="n"/>
@@ -7701,7 +7705,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-017</t>
+          <t>SWR-TRN-019</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -7711,7 +7715,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-006, SYS-SR-024</t>
+          <t>SYS-SR-023</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -7719,17 +7723,13 @@
           <t>RoverPlatformArch/.../rover_transport</t>
         </is>
       </c>
-      <c r="E234" s="3" t="inlineStr">
-        <is>
-          <t>rover_transport/rover_modbus_driver/test/unit/test_modbus_discrete_io_client.cpp; rover_transport/rover_modbus_driver/test/integration/test_modbus_tcp_transport.cpp</t>
-        </is>
-      </c>
+      <c r="E234" s="3" t="n"/>
       <c r="F234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-018</t>
+          <t>SWR-TRN-020</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -7747,17 +7747,13 @@
           <t>RoverPlatformArch/.../rover_transport</t>
         </is>
       </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>rover_transport/rover_modbus_driver/test/unit/test_modbus_discrete_io_client.cpp; rover_transport/rover_modbus_driver/test/unit/test_modbus_discrete_io_client_failures.cpp; rover_transport/rover_modbus_driver/test/e2e/test_modbus_tcp_reply_handling.cpp</t>
-        </is>
-      </c>
+      <c r="E235" s="3" t="n"/>
       <c r="F235" s="3" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-019</t>
+          <t>SWR-TRN-021</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -7767,7 +7763,7 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-023</t>
+          <t>SYS-SR-022</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -7781,7 +7777,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-020</t>
+          <t>SWR-TRN-022</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -7791,7 +7787,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-007, SYS-SR-023</t>
+          <t>SYS-SR-020</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -7799,13 +7795,17 @@
           <t>RoverPlatformArch/.../rover_transport</t>
         </is>
       </c>
-      <c r="E237" s="3" t="n"/>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>rover_transport/rover_modbus_driver/scripts/check_core_purity.sh</t>
+        </is>
+      </c>
       <c r="F237" s="3" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-021</t>
+          <t>SWR-TRN-023</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-022</t>
+          <t>SYS-SR-005</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -7823,41 +7823,41 @@
           <t>RoverPlatformArch/.../rover_transport</t>
         </is>
       </c>
-      <c r="E238" s="3" t="n"/>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>rover_transport/rover_udp_driver/test/integration/test_asio_udp_socket.cpp; rover_transport/rover_udp_driver/test/integration/test_udp_nodes_lifecycle.cpp; rover_crsf_teleop/test/e2e/test_teleop_launch.py</t>
+        </is>
+      </c>
       <c r="F238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>SWR-TRN-022</t>
+          <t>SWR-MUX-001</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>rover_transport</t>
+          <t>rover_twist_mux</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-020</t>
+          <t>SYS-SR-005</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>RoverPlatformArch/.../rover_transport</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>rover_transport/rover_modbus_driver/scripts/check_core_purity.sh</t>
-        </is>
-      </c>
+          <t>RoverPlatformArch/.../rover_twist_mux</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="n"/>
       <c r="F239" s="3" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-001</t>
+          <t>SWR-MUX-002</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -7875,13 +7875,21 @@
           <t>RoverPlatformArch/.../rover_twist_mux</t>
         </is>
       </c>
-      <c r="E240" s="3" t="n"/>
-      <c r="F240" s="3" t="n"/>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>rover_twist_mux/test/unit/test_twist_mux_priorities.py</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>tCommandArbitration/testPriorityOrder</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-002</t>
+          <t>SWR-MUX-003</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -7891,7 +7899,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-005</t>
+          <t>SYS-SR-011, SYS-SR-012</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -7899,21 +7907,17 @@
           <t>RoverPlatformArch/.../rover_twist_mux</t>
         </is>
       </c>
-      <c r="E241" s="3" t="inlineStr">
-        <is>
-          <t>rover_twist_mux/test/unit/test_twist_mux_priorities.py</t>
-        </is>
-      </c>
+      <c r="E241" s="3" t="n"/>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>tCommandArbitration/testPriorityOrder</t>
+          <t>tCommandArbitration/testPriorityOrder; tCommandArbitration/testCommandWatchdog</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-003</t>
+          <t>SWR-MUX-004</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -7923,7 +7927,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-011, SYS-SR-012</t>
+          <t>SYS-SR-006, SYS-SR-007, SYS-SR-008</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -7931,17 +7935,21 @@
           <t>RoverPlatformArch/.../rover_twist_mux</t>
         </is>
       </c>
-      <c r="E242" s="3" t="n"/>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>rover_twist_mux/test/unit/test_twist_mux_priorities.py</t>
+        </is>
+      </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>tCommandArbitration/testPriorityOrder; tCommandArbitration/testCommandWatchdog</t>
+          <t>tCommandArbitration/testMotionLockMasksAllSources</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-004</t>
+          <t>SWR-MUX-005</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -7951,7 +7959,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-006, SYS-SR-007, SYS-SR-008</t>
+          <t>SYS-SR-007, SYS-SR-023</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -7961,19 +7969,15 @@
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>rover_twist_mux/test/unit/test_twist_mux_priorities.py</t>
-        </is>
-      </c>
-      <c r="F243" s="3" t="inlineStr">
-        <is>
-          <t>tCommandArbitration/testMotionLockMasksAllSources</t>
-        </is>
-      </c>
+          <t>rover_twist_mux/test/integration/test_motion_lock_node.cpp</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-005</t>
+          <t>SWR-MUX-006</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7983,7 +7987,7 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-007, SYS-SR-023</t>
+          <t>SYS-SR-023</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -8001,7 +8005,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-006</t>
+          <t>SWR-MUX-007</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -8011,7 +8015,7 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-023</t>
+          <t>SYS-SR-006, SYS-SR-007</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -8021,15 +8025,19 @@
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>rover_twist_mux/test/integration/test_motion_lock_node.cpp</t>
-        </is>
-      </c>
-      <c r="F245" s="3" t="n"/>
+          <t>rover_twist_mux/test/integration/test_motion_lock_node.cpp; rover_twist_mux/test/unit/test_motion_lock_health.cpp; rover_twist_mux/test/unit/test_motion_lock_policy.cpp</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>tCommandArbitration/testLockedAtStartup</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-007</t>
+          <t>SWR-MUX-008</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -8039,7 +8047,7 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-006, SYS-SR-007</t>
+          <t>SYS-SR-007, SYS-SR-023</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -8049,19 +8057,19 @@
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>rover_twist_mux/test/integration/test_motion_lock_node.cpp; rover_twist_mux/test/unit/test_motion_lock_health.cpp; rover_twist_mux/test/unit/test_motion_lock_policy.cpp</t>
+          <t>rover_twist_mux/test/integration/test_motion_lock_node.cpp; rover_twist_mux/test/unit/test_motion_lock_health.cpp</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>tCommandArbitration/testLockedAtStartup</t>
+          <t>tCommandArbitration/testStaleSafetyLocks</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-008</t>
+          <t>SWR-MUX-009</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -8071,7 +8079,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-007, SYS-SR-023</t>
+          <t>SYS-SR-006, SYS-SR-007</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -8084,16 +8092,12 @@
           <t>rover_twist_mux/test/integration/test_motion_lock_node.cpp; rover_twist_mux/test/unit/test_motion_lock_health.cpp</t>
         </is>
       </c>
-      <c r="F247" s="3" t="inlineStr">
-        <is>
-          <t>tCommandArbitration/testStaleSafetyLocks</t>
-        </is>
-      </c>
+      <c r="F247" s="3" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-009</t>
+          <t>SWR-MUX-010</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -8103,7 +8107,7 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-006, SYS-SR-007</t>
+          <t>SYS-SR-006, SYS-SR-007, SYS-SR-008</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -8113,15 +8117,19 @@
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>rover_twist_mux/test/integration/test_motion_lock_node.cpp; rover_twist_mux/test/unit/test_motion_lock_health.cpp</t>
-        </is>
-      </c>
-      <c r="F248" s="3" t="n"/>
+          <t>rover_twist_mux/test/unit/test_motion_lock_policy.cpp; rover_twist_mux/test/unit/test_motion_lock_health.cpp; rover_twist_mux/test/integration/test_motion_lock_node.cpp</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>tCommandArbitration/testMotionLockMasksAllSources</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-010</t>
+          <t>SWR-MUX-011</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -8129,11 +8137,7 @@
           <t>rover_twist_mux</t>
         </is>
       </c>
-      <c r="C249" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-006, SYS-SR-007, SYS-SR-008</t>
-        </is>
-      </c>
+      <c r="C249" s="3" t="n"/>
       <c r="D249" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_twist_mux</t>
@@ -8141,19 +8145,15 @@
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>rover_twist_mux/test/unit/test_motion_lock_policy.cpp; rover_twist_mux/test/unit/test_motion_lock_health.cpp; rover_twist_mux/test/integration/test_motion_lock_node.cpp</t>
-        </is>
-      </c>
-      <c r="F249" s="3" t="inlineStr">
-        <is>
-          <t>tCommandArbitration/testMotionLockMasksAllSources</t>
-        </is>
-      </c>
+          <t>rover_twist_mux/test/unit/test_motion_lock_policy.cpp</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-011</t>
+          <t>SWR-MUX-012</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -8167,17 +8167,13 @@
           <t>RoverPlatformArch/.../rover_twist_mux</t>
         </is>
       </c>
-      <c r="E250" s="3" t="inlineStr">
-        <is>
-          <t>rover_twist_mux/test/unit/test_motion_lock_policy.cpp</t>
-        </is>
-      </c>
+      <c r="E250" s="3" t="n"/>
       <c r="F250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-012</t>
+          <t>SWR-MUX-013</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -8185,19 +8181,27 @@
           <t>rover_twist_mux</t>
         </is>
       </c>
-      <c r="C251" s="3" t="n"/>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-022</t>
+        </is>
+      </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_twist_mux</t>
         </is>
       </c>
-      <c r="E251" s="3" t="n"/>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>rover_twist_mux/test/unit/test_motion_lock_health.cpp</t>
+        </is>
+      </c>
       <c r="F251" s="3" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-013</t>
+          <t>SWR-MUX-014</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -8207,7 +8211,7 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-022</t>
+          <t>SYS-SR-011, SYS-SR-012</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -8217,7 +8221,7 @@
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>rover_twist_mux/test/unit/test_motion_lock_health.cpp</t>
+          <t>rover_twist_mux/test/unit/test_command_freshness_filter.cpp; rover_twist_mux/test/integration/test_command_freshness_node.cpp</t>
         </is>
       </c>
       <c r="F252" s="3" t="n"/>
@@ -8225,7 +8229,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-014</t>
+          <t>SWR-MUX-015</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -8235,7 +8239,7 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-011, SYS-SR-012</t>
+          <t>SYS-SR-011</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -8245,7 +8249,7 @@
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>rover_twist_mux/test/unit/test_command_freshness_filter.cpp; rover_twist_mux/test/integration/test_command_freshness_node.cpp</t>
+          <t>rover_twist_mux/test/unit/test_command_freshness_filter.cpp</t>
         </is>
       </c>
       <c r="F253" s="3" t="n"/>
@@ -8253,7 +8257,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-015</t>
+          <t>SWR-MUX-016</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -8263,7 +8267,7 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-011</t>
+          <t>SYS-SR-005</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -8273,7 +8277,7 @@
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>rover_twist_mux/test/unit/test_command_freshness_filter.cpp</t>
+          <t>rover_twist_mux/test/integration/test_command_freshness_node.cpp</t>
         </is>
       </c>
       <c r="F254" s="3" t="n"/>
@@ -8281,7 +8285,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-016</t>
+          <t>SWR-MUX-017</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -8289,27 +8293,19 @@
           <t>rover_twist_mux</t>
         </is>
       </c>
-      <c r="C255" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-005</t>
-        </is>
-      </c>
+      <c r="C255" s="3" t="n"/>
       <c r="D255" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_twist_mux</t>
         </is>
       </c>
-      <c r="E255" s="3" t="inlineStr">
-        <is>
-          <t>rover_twist_mux/test/integration/test_command_freshness_node.cpp</t>
-        </is>
-      </c>
+      <c r="E255" s="3" t="n"/>
       <c r="F255" s="3" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-017</t>
+          <t>SWR-MUX-018</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -8317,7 +8313,11 @@
           <t>rover_twist_mux</t>
         </is>
       </c>
-      <c r="C256" s="3" t="n"/>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>SYS-SR-022</t>
+        </is>
+      </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
           <t>RoverPlatformArch/.../rover_twist_mux</t>
@@ -8329,7 +8329,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-018</t>
+          <t>SWR-MUX-019</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-022</t>
+          <t>SYS-SR-007</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -8353,7 +8353,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>SWR-MUX-019</t>
+          <t>SWR-MUX-020</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>SYS-SR-007</t>
+          <t>SYS-SR-010</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -8372,38 +8372,14 @@
         </is>
       </c>
       <c r="E258" s="3" t="n"/>
-      <c r="F258" s="3" t="n"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="3" t="inlineStr">
-        <is>
-          <t>SWR-MUX-020</t>
-        </is>
-      </c>
-      <c r="B259" s="3" t="inlineStr">
-        <is>
-          <t>rover_twist_mux</t>
-        </is>
-      </c>
-      <c r="C259" s="3" t="inlineStr">
-        <is>
-          <t>SYS-SR-010</t>
-        </is>
-      </c>
-      <c r="D259" s="3" t="inlineStr">
-        <is>
-          <t>RoverPlatformArch/.../rover_twist_mux</t>
-        </is>
-      </c>
-      <c r="E259" s="3" t="n"/>
-      <c r="F259" s="3" t="inlineStr">
+      <c r="F258" s="3" t="inlineStr">
         <is>
           <t>tPlatformModeManager/testTeleopAutonomousFollowActiveSource</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F259"/>
+  <autoFilter ref="A1:F258"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>